--- a/03_quotation/quotation_metadata.xlsx
+++ b/03_quotation/quotation_metadata.xlsx
@@ -374,7 +374,7 @@
         <x:v>최종 합계 (부가세 포함): 8,420,000원</x:v>
       </x:c>
       <x:c r="K2" s="3" t="str">
-        <x:v>인테리어_견적서_최종.png</x:v>
+        <x:v>인테리어_견적서_최종.jpg</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="90" customHeight="1">
@@ -409,7 +409,7 @@
         <x:v>최종 합계 (부가세 포함): 12,700,000원</x:v>
       </x:c>
       <x:c r="K3" s="3" t="str">
-        <x:v>사무실이전_견적_v3.png</x:v>
+        <x:v>사무실이전_견적_v3.jpg</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="90" customHeight="1">
@@ -444,7 +444,7 @@
         <x:v>최종 합계 (부가세 포함): 6,150,000원</x:v>
       </x:c>
       <x:c r="K4" s="3" t="str">
-        <x:v>촬영장비_렌탈견적.png</x:v>
+        <x:v>촬영장비_렌탈견적.jpg</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="90" customHeight="1">
@@ -479,7 +479,7 @@
         <x:v>최종 합계 (부가세 포함): 5,500,000원</x:v>
       </x:c>
       <x:c r="K5" s="3" t="str">
-        <x:v>웹사이트_구축제안견적.png</x:v>
+        <x:v>웹사이트_구축제안견적.jpg</x:v>
       </x:c>
     </x:row>
     <x:row r="7">

--- a/03_quotation/quotation_metadata.xlsx
+++ b/03_quotation/quotation_metadata.xlsx
@@ -2,7 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="문서별 메타데이터" sheetId="1" r:id="Rfe601165d1bf4cf7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="문서별 메타데이터" sheetId="1" r:id="R28706265f6944e36"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="표시 방식" sheetId="2" r:id="Reb0e73fd28b94b57"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -17,7 +18,7 @@
     <x:numFmt numFmtId="200" formatCode="yyyy-mm-dd"/>
     <x:numFmt numFmtId="201" formatCode="#,##0"/>
   </x:numFmts>
-  <x:fonts count="3">
+  <x:fonts count="5">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -32,8 +33,18 @@
       <x:color rgb="FFFFFFFF"/>
       <x:name val="Noto Sans KR"/>
     </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:name val="Droid Sans Fallback"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Droid Sans Fallback"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="3">
+  <x:fills count="4">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -45,6 +56,11 @@
         <x:fgColor rgb="FF26374A"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF294563"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="1">
     <x:border/>
@@ -52,7 +68,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="8">
+  <x:cellXfs count="13">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -71,6 +87,19 @@
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="201" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -339,7 +368,7 @@
         <x:v>검색 근거</x:v>
       </x:c>
       <x:c r="K1" s="5" t="str">
-        <x:v>썸네일 파일명</x:v>
+        <x:v>미리보기 이미지</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="90" customHeight="1">
@@ -368,13 +397,13 @@
         <x:v>주거 공간 부분 리모델링에 대한 견적서. 부가세 포함 최종 합계는 8,420,000원이다.</x:v>
       </x:c>
       <x:c r="I2" s="3" t="str">
-        <x:v>상위</x:v>
+        <x:v>함께 제공</x:v>
       </x:c>
       <x:c r="J2" s="3" t="str">
         <x:v>최종 합계 (부가세 포함): 8,420,000원</x:v>
       </x:c>
       <x:c r="K2" s="3" t="str">
-        <x:v>인테리어_견적서_최종.jpg</x:v>
+        <x:v>인테리어_견적서_최종.png</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="90" customHeight="1">
@@ -403,18 +432,18 @@
         <x:v>40석 사무실 이전 / 약 150㎡에 대한 견적서. 부가세 포함 최종 합계는 12,700,000원이다.</x:v>
       </x:c>
       <x:c r="I3" s="3" t="str">
-        <x:v>상위</x:v>
+        <x:v>함께 제공</x:v>
       </x:c>
       <x:c r="J3" s="3" t="str">
         <x:v>최종 합계 (부가세 포함): 12,700,000원</x:v>
       </x:c>
       <x:c r="K3" s="3" t="str">
-        <x:v>사무실이전_견적_v3.jpg</x:v>
+        <x:v>사무실이전_견적_v3.png</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="90" customHeight="1">
       <x:c r="A4" s="3" t="str">
-        <x:v>촬영장비_렌탈견적.pdf</x:v>
+        <x:v>IMG_008426.png</x:v>
       </x:c>
       <x:c r="B4" s="6" t="n">
         <x:v>45938</x:v>
@@ -432,19 +461,19 @@
         <x:v>예</x:v>
       </x:c>
       <x:c r="G4" s="3" t="str">
-        <x:v>견적서, 촬영장비, 렌탈, 영상 제작</x:v>
+        <x:v>견적서, 촬영장비, 렌탈, 영상 제작, 스크린샷</x:v>
       </x:c>
       <x:c r="H4" s="3" t="str">
-        <x:v>브랜드 영상 촬영 장비 / 2일에 대한 견적서. 부가세 포함 최종 합계는 6,150,000원이다.</x:v>
+        <x:v>촬영장비 렌탈 견적서 화면을 저장한 스크린샷. 이미지 속 최종 합계는 부가세 포함 6,150,000원이다.</x:v>
       </x:c>
       <x:c r="I4" s="3" t="str">
-        <x:v>상위</x:v>
+        <x:v>함께 제공</x:v>
       </x:c>
       <x:c r="J4" s="3" t="str">
         <x:v>최종 합계 (부가세 포함): 6,150,000원</x:v>
       </x:c>
       <x:c r="K4" s="3" t="str">
-        <x:v>촬영장비_렌탈견적.jpg</x:v>
+        <x:v>IMG_008426.png</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="90" customHeight="1">
@@ -473,13 +502,13 @@
         <x:v>기업 소개 반응형 웹사이트에 대한 견적서. 부가세 포함 최종 합계는 5,500,000원이다.</x:v>
       </x:c>
       <x:c r="I5" s="3" t="str">
-        <x:v>상위</x:v>
+        <x:v>함께 제공</x:v>
       </x:c>
       <x:c r="J5" s="3" t="str">
         <x:v>최종 합계 (부가세 포함): 5,500,000원</x:v>
       </x:c>
       <x:c r="K5" s="3" t="str">
-        <x:v>웹사이트_구축제안견적.jpg</x:v>
+        <x:v>웹사이트_구축제안견적.png</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -490,7 +519,129 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5a86c96379d44720"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R782cbe58e4e54c97"/>
   </x:tableParts>
 </x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="37" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="13" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="24" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="38" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="31" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="30" customHeight="1">
+      <x:c r="A1" s="12" t="str">
+        <x:v>현재 파일명</x:v>
+      </x:c>
+      <x:c r="B1" s="12" t="str">
+        <x:v>파일 형식</x:v>
+      </x:c>
+      <x:c r="C1" s="12" t="str">
+        <x:v>결과 형태</x:v>
+      </x:c>
+      <x:c r="D1" s="12" t="str">
+        <x:v>목록 표시</x:v>
+      </x:c>
+      <x:c r="E1" s="12" t="str">
+        <x:v>미리보기 이미지</x:v>
+      </x:c>
+      <x:c r="F1" s="12" t="str">
+        <x:v>검색 방식</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" ht="46" customHeight="1">
+      <x:c r="A2" s="10" t="str">
+        <x:v>인테리어_견적서_최종.pdf</x:v>
+      </x:c>
+      <x:c r="B2" s="10" t="str">
+        <x:v>pdf</x:v>
+      </x:c>
+      <x:c r="C2" s="10" t="str">
+        <x:v>문서</x:v>
+      </x:c>
+      <x:c r="D2" s="10" t="str">
+        <x:v>파일유형 아이콘</x:v>
+      </x:c>
+      <x:c r="E2" s="10" t="str">
+        <x:v>인테리어_견적서_최종.png</x:v>
+      </x:c>
+      <x:c r="F2" s="10" t="str">
+        <x:v>문서 본문·금액 읽기</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="46" customHeight="1">
+      <x:c r="A3" s="10" t="str">
+        <x:v>사무실이전_견적_v3.xlsx</x:v>
+      </x:c>
+      <x:c r="B3" s="10" t="str">
+        <x:v>xlsx</x:v>
+      </x:c>
+      <x:c r="C3" s="10" t="str">
+        <x:v>문서</x:v>
+      </x:c>
+      <x:c r="D3" s="10" t="str">
+        <x:v>파일유형 아이콘</x:v>
+      </x:c>
+      <x:c r="E3" s="10" t="str">
+        <x:v>사무실이전_견적_v3.png</x:v>
+      </x:c>
+      <x:c r="F3" s="10" t="str">
+        <x:v>문서 본문·금액 읽기</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="46" customHeight="1">
+      <x:c r="A4" s="10" t="str">
+        <x:v>IMG_008426.png</x:v>
+      </x:c>
+      <x:c r="B4" s="10" t="str">
+        <x:v>png</x:v>
+      </x:c>
+      <x:c r="C4" s="10" t="str">
+        <x:v>스크린샷</x:v>
+      </x:c>
+      <x:c r="D4" s="10" t="str">
+        <x:v>이미지 썸네일</x:v>
+      </x:c>
+      <x:c r="E4" s="10" t="str">
+        <x:v>IMG_008426.png</x:v>
+      </x:c>
+      <x:c r="F4" s="10" t="str">
+        <x:v>이미지 속 글·금액 읽기</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="46" customHeight="1">
+      <x:c r="A5" s="10" t="str">
+        <x:v>웹사이트_구축제안견적.pdf</x:v>
+      </x:c>
+      <x:c r="B5" s="10" t="str">
+        <x:v>pdf</x:v>
+      </x:c>
+      <x:c r="C5" s="10" t="str">
+        <x:v>문서</x:v>
+      </x:c>
+      <x:c r="D5" s="10" t="str">
+        <x:v>파일유형 아이콘</x:v>
+      </x:c>
+      <x:c r="E5" s="10" t="str">
+        <x:v>웹사이트_구축제안견적.png</x:v>
+      </x:c>
+      <x:c r="F5" s="10" t="str">
+        <x:v>문서 본문·금액 읽기</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" t="str">
+        <x:v>총 4개: 문서 3개 + 스크린샷 1개. 파일명과 파일 형식에 제한 없이 내용을 읽어 검색한다.</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
 </file>